--- a/data/ams_weekly_data/White_Mulberry/ads_report_week15.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week15.xlsx
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>29872.7</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week15.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week15.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
